--- a/data/output/2025/evaluasi_62.xlsx
+++ b/data/output/2025/evaluasi_62.xlsx
@@ -1577,7 +1577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1721,6 +1721,314 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8.551342166943337</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>36.82375075148097</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.04347981890043</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.144630857771233</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.584586189237116</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.19678270578227</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.427698955868892</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.405312162513598</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.3666055232044659</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Kapuas</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.1037004309553321</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1735,7 +2043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,6 +2131,314 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-3 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7.002072677382494</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>40.08111890221743</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.19453351685546</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3.315920813103565</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.602306722389746</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.149178923242352</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.576271218324812</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.2426178927941333</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.429351159648921</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.0695048504718114</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1837,7 +2453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1981,6 +2597,314 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.860932112384234</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>35.56245582919243</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16.83802376475252</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.450468677309956</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4291817240153626</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.496024279273712</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.703290597190772</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Selatan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.152852368026264</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Selatan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.1698763332991274</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Selatan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-2.583444298016133</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1995,7 +2919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2125,18 +3049,326 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>2.269958648506464</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6207</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Lamandau</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.761130077848682</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6207</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Lamandau</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.373939465598058</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6207</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Lamandau</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6207</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Lamandau</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.31826566858862</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6207</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Lamandau</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4.683057872170422</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6207</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Lamandau</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5.008626640455847</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6207</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Lamandau</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4.152934235453754</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6207</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Lamandau</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-2.653399818587316</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6207</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Lamandau</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>8.906035585482286</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6207</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Lamandau</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>8.486736191533877</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6207</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Lamandau</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>-2.37417262748212</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2153,7 +3385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2297,6 +3529,286 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.098872507661008</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8.862747999999993</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4.297966472658511</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8.501643554786439</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5.254909937719115</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.2716279999999947</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.2755171838080284</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.652090144348751</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_2025_prov vs implisit_y-on-y_pkrt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Seruyan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6.841785124467868</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2311,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2371,6 +3883,342 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.944313699965099</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.089544713282095</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.56812151783088</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.542581598379373</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.850262457785054</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4.75197733168465</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.021211436431149</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5560988963372189</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.173293491921697</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.1168458908462477</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Murung Raya</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7.271197570323305</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2385,7 +4233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2529,6 +4377,314 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6205</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.77793525775037</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6205</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2873068122012572</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6205</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.03621048562208</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6205</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.437044187620303</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6205</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6205</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6.4366971468193</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6205</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Utara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8.525484301005529</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6205</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Utara</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.709199843372098</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6205</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Utara</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.507720094966026</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6205</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Utara</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5.776067515661219</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6205</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Utara</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.8821751419589935</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2543,7 +4699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2799,6 +4955,342 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6206</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukamara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.519082292566465</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6206</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukamara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4359309927001494</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6206</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukamara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3.823951347266226</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6206</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukamara</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3997484420925175</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6206</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukamara</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6206</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukamara</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3.079369540283262</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6206</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukamara</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.620926337350815</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6206</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukamara</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6.001785210759071</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6206</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukamara</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.645694319192685</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6206</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukamara</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.241322608367687</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6206</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukamara</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-2.956476467441478</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6206</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukamara</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.0223786048349068</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2813,7 +5305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3349,6 +5841,314 @@
       <c r="F19" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.4665235188227984</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-20.0004335701041</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10.72542460816006</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>8.744302047902021</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-17.44530028701481</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>6.345847161130512</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.8031359719297646</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-38.90674391774479</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.3878729788707582</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kabupaten Katingan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>5.894448810745557</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3363,7 +6163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3675,6 +6475,342 @@
       <c r="F11" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.242377458042352</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.273412390622376</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.6517591371167</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3377752329657069</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3.106439885935195</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4.068967479499641</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4.538669668161964</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2.032812698745681</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.2167379240993969</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.1624762456939614</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6212</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Timur</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>8.819836045169351</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3689,7 +6825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3903,20 +7039,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-12.9834440637662</v>
+        <v>0.2282088653476035</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3931,18 +7067,298 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>1.190066053344559</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.797582095534923</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.36600449368853</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.9679719651528979</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.345120842176606</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4.488463754200258</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.351148186862507</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.42506205781877</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-12.9834440637662</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>-7.846017826070464</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3959,7 +7375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4047,6 +7463,398 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.960363794100099</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9199999999998999</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.00999999999987</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.567707623061386</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5.023940991484635</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.324416055253935</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7.022751790877245</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.943101507744069</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.479999999999738</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.653391179919518</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.7528033729470285</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7.336286710928674</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kota Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.85051093203929</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4061,7 +7869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4233,6 +8041,314 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.319482054344242</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>40.72922675401538</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Barat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.03144167619363</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Barat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Barat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.584571847430751</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Barat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.692657930209971</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Barat</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.178651371619127</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Barat</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.584746283192089</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Barat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.804503351388961</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Barat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.5652008215936807</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotawaringin Barat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.4281452467904712</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4247,7 +8363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4366,6 +8482,314 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6211</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunung Mas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.172958500215455</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6211</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunung Mas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.3396509910308739</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6211</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunung Mas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6211</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunung Mas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.76972238390348</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6211</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunung Mas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>37.37368273330845</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6211</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunung Mas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.085818803118357</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6211</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunung Mas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.515815003869282</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6211</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunung Mas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>20.24941327634333</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6211</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunung Mas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6.764611056194234</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6211</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunung Mas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.364447454065796</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6211</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunung Mas</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>8.595806450378685</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
